--- a/program/ConstructionResults.xlsx
+++ b/program/ConstructionResults.xlsx
@@ -1,31 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Palych\Desktop\PAROGENA\program\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\PAROGENA\program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83BE8741-2C56-4951-948E-13C3CDA48C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8D3BF33-1DCF-4592-878A-26CB0DE56349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9375" yWindow="1785" windowWidth="28800" windowHeight="11295"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="472" uniqueCount="35">
   <si>
     <t>Величина</t>
   </si>
@@ -87,7 +82,7 @@
     <t>Dкорп</t>
   </si>
   <si>
-    <t>DD</t>
+    <t>ΔD</t>
   </si>
   <si>
     <t>Zкор</t>
@@ -123,26 +118,30 @@
     <t>шт.</t>
   </si>
   <si>
+    <t>м</t>
+  </si>
+  <si>
     <t>%</t>
   </si>
   <si>
-    <t>шт</t>
-  </si>
-  <si>
     <t>Скорость теплоносителя, м/с</t>
-  </si>
-  <si>
-    <t>м</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -153,7 +152,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -161,17 +160,88 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="true"/>
+      </left>
+      <right style="thin">
+        <color auto="true"/>
+      </right>
+      <top style="thin">
+        <color auto="true"/>
+      </top>
+      <bottom style="thin">
+        <color auto="true"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -185,7 +255,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
     <a:clrScheme name="Стандартная">
       <a:dk1>
@@ -336,7 +406,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -360,9 +430,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -386,7 +456,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -421,7 +491,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -439,7 +509,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -464,7 +534,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -500,778 +570,808 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="27.85546875" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="8" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="true"/>
+    <col min="2" max="2" width="19.7109375" customWidth="true"/>
+    <col min="3" max="3" width="28" bestFit="true" customWidth="true"/>
+    <col min="4" max="4" width="6.140625" bestFit="true" customWidth="true"/>
+    <col min="5" max="5" width="6.140625" bestFit="true" customWidth="true"/>
+    <col min="6" max="6" width="6.140625" bestFit="true" customWidth="true"/>
+    <col min="7" max="7" width="6.140625" bestFit="true" customWidth="true"/>
+    <col min="8" max="8" width="6.140625" bestFit="true" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C1" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>2.5</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>3</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>3.5</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>4</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>4.5</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3">
-        <v>21.6</v>
-      </c>
-      <c r="D3">
-        <v>21.6</v>
-      </c>
-      <c r="E3">
-        <v>21.6</v>
-      </c>
-      <c r="F3">
-        <v>21.6</v>
-      </c>
-      <c r="G3">
-        <v>21.6</v>
-      </c>
-      <c r="H3">
-        <v>21.6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="4">
+        <v>21.600000000000001</v>
+      </c>
+      <c r="D3" s="4">
+        <v>21.600000000000001</v>
+      </c>
+      <c r="E3" s="4">
+        <v>21.600000000000001</v>
+      </c>
+      <c r="F3" s="4">
+        <v>21.600000000000001</v>
+      </c>
+      <c r="G3" s="4">
+        <v>21.600000000000001</v>
+      </c>
+      <c r="H3" s="4">
+        <v>21.600000000000001</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4">
+      <c r="B4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="4">
         <v>24</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="4">
         <v>24</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="4">
         <v>24</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="4">
         <v>24</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="4">
         <v>24</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="4">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5">
-        <v>21.6</v>
-      </c>
-      <c r="D5">
-        <v>21.6</v>
-      </c>
-      <c r="E5">
-        <v>21.6</v>
-      </c>
-      <c r="F5">
-        <v>21.6</v>
-      </c>
-      <c r="G5">
-        <v>21.6</v>
-      </c>
-      <c r="H5">
-        <v>21.6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="4">
+        <v>21.600000000000001</v>
+      </c>
+      <c r="D5" s="4">
+        <v>21.600000000000001</v>
+      </c>
+      <c r="E5" s="4">
+        <v>21.600000000000001</v>
+      </c>
+      <c r="F5" s="4">
+        <v>21.600000000000001</v>
+      </c>
+      <c r="G5" s="4">
+        <v>21.600000000000001</v>
+      </c>
+      <c r="H5" s="4">
+        <v>21.600000000000001</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="4">
         <v>15960</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="4">
         <v>13320</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="4">
         <v>11400</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="4">
         <v>9960</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="4">
         <v>8880</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="4">
         <v>8040</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="4">
         <v>120</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="4">
         <v>120</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="4">
         <v>120</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="4">
         <v>120</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="4">
         <v>120</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="4">
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="4">
         <v>133</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="4">
         <v>111</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="4">
         <v>95</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="4">
         <v>83</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="4">
         <v>74</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="4">
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9">
-        <v>7.702455240241199</v>
-      </c>
-      <c r="D9">
-        <v>8.8389342447445145</v>
-      </c>
-      <c r="E9">
-        <v>9.9900885040387859</v>
-      </c>
-      <c r="F9">
-        <v>11.135725867123746</v>
-      </c>
-      <c r="G9">
-        <v>12.222468997814962</v>
-      </c>
-      <c r="H9">
-        <v>13.257374805930988</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="5">
+        <v>7.7918110583391007</v>
+      </c>
+      <c r="D9" s="5">
+        <v>8.94625441732612</v>
+      </c>
+      <c r="E9" s="5">
+        <v>10.115715250031071</v>
+      </c>
+      <c r="F9" s="5">
+        <v>11.279728950072325</v>
+      </c>
+      <c r="G9" s="5">
+        <v>12.384183505752892</v>
+      </c>
+      <c r="H9" s="5">
+        <v>13.436168418639737</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10">
-        <v>12.585213827902979</v>
-      </c>
-      <c r="D10">
-        <v>13.111128704792506</v>
-      </c>
-      <c r="E10">
-        <v>13.830389181185236</v>
-      </c>
-      <c r="F10">
-        <v>14.976026544270194</v>
-      </c>
-      <c r="G10">
-        <v>16.062769674961412</v>
-      </c>
-      <c r="H10">
-        <v>17.097675483077438</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="5">
+        <v>12.674569646000879</v>
+      </c>
+      <c r="D10" s="5">
+        <v>13.218448877374112</v>
+      </c>
+      <c r="E10" s="5">
+        <v>13.956015927177521</v>
+      </c>
+      <c r="F10" s="5">
+        <v>15.120029627218774</v>
+      </c>
+      <c r="G10" s="5">
+        <v>16.224484182899342</v>
+      </c>
+      <c r="H10" s="5">
+        <v>17.276469095786187</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11">
-        <v>6.4166966525794189</v>
-      </c>
-      <c r="D11">
-        <v>7.6887397846965229</v>
-      </c>
-      <c r="E11">
-        <v>8.9357878268923372</v>
-      </c>
-      <c r="F11">
-        <v>10.081425189977297</v>
-      </c>
-      <c r="G11">
-        <v>11.168168320668514</v>
-      </c>
-      <c r="H11">
-        <v>12.203074128784539</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="5">
+        <v>6.5060524706773206</v>
+      </c>
+      <c r="D11" s="5">
+        <v>7.7960599572781284</v>
+      </c>
+      <c r="E11" s="5">
+        <v>9.0614145728846225</v>
+      </c>
+      <c r="F11" s="5">
+        <v>10.225428272925877</v>
+      </c>
+      <c r="G11" s="5">
+        <v>11.329882828606443</v>
+      </c>
+      <c r="H11" s="5">
+        <v>12.381867741493288</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12">
-        <v>11377</v>
-      </c>
-      <c r="D12">
-        <v>12222</v>
-      </c>
-      <c r="E12">
-        <v>13167</v>
-      </c>
-      <c r="F12">
-        <v>14312</v>
-      </c>
-      <c r="G12">
-        <v>15399</v>
-      </c>
-      <c r="H12">
-        <v>16434</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="4">
+        <v>11466</v>
+      </c>
+      <c r="D12" s="4">
+        <v>12329</v>
+      </c>
+      <c r="E12" s="4">
+        <v>13292</v>
+      </c>
+      <c r="F12" s="4">
+        <v>14456</v>
+      </c>
+      <c r="G12" s="4">
+        <v>15561</v>
+      </c>
+      <c r="H12" s="4">
+        <v>16613</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13">
+      <c r="B13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="4">
         <v>450</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="4">
         <v>450</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="4">
         <v>450</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="4">
         <v>450</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="4">
         <v>450</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="4">
         <v>450</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14">
+      <c r="B14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="4">
         <v>450</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="4">
         <v>450</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="4">
         <v>450</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="4">
         <v>450</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="4">
         <v>450</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="4">
         <v>450</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15">
+      <c r="B15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="4">
         <v>2867</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="4">
         <v>2392</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="4">
         <v>2046</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="4">
         <v>1787</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="4">
         <v>1593</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="4">
         <v>1442</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16">
+      <c r="B16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="4">
         <v>200</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="4">
         <v>200</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="4">
         <v>200</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="4">
         <v>200</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="4">
         <v>200</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="4">
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17">
+      <c r="B17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="4">
         <v>600</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="4">
         <v>600</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="4">
         <v>600</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="4">
         <v>600</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="4">
         <v>600</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="4">
         <v>600</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18">
+      <c r="B18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="4">
         <v>400</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="4">
         <v>400</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="4">
         <v>400</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="4">
         <v>400</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="4">
         <v>400</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="4">
         <v>400</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B19" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19">
+      <c r="B19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="4">
         <v>3706</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="4">
         <v>3706</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="4">
         <v>3706</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="4">
         <v>3706</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="4">
         <v>3706</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="4">
         <v>3706</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B20" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20">
+      <c r="B20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="4">
         <v>4517</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="4">
         <v>4042</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="4">
         <v>3696</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="4">
         <v>3437</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="4">
         <v>3243</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="4">
         <v>3092</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B21" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21">
+      <c r="B21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="4">
         <v>4517</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="4">
         <v>4042</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="4">
         <v>3706</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="4">
         <v>3706</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="4">
         <v>3706</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="4">
         <v>3706</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22">
+      <c r="B22" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="5">
         <v>17.954394509630287</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="5">
         <v>7.4385654195262347</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="5">
         <v>0.22138587558113793</v>
       </c>
-      <c r="F22">
-        <v>5.9552800531326104</v>
-      </c>
-      <c r="G22">
+      <c r="F22" s="5">
+        <v>5.9552800531326105</v>
+      </c>
+      <c r="G22" s="5">
         <v>10.250166039406686</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="5">
         <v>13.593092760681868</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23">
+      <c r="B23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="4">
         <v>3</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="4">
         <v>3</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="4">
         <v>3</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="4">
         <v>3</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="4">
         <v>3</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C24">
+      <c r="B24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="4">
         <v>130</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="4">
         <v>130</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="4">
         <v>130</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="4">
         <v>130</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="4">
         <v>130</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="4">
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B25" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25">
+      <c r="B25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="4">
         <v>230</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="4">
         <v>230</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="4">
         <v>230</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="4">
         <v>230</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="4">
         <v>230</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="4">
         <v>230</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26">
+      <c r="B26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="4">
         <v>903</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="4">
         <v>808</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="4">
         <v>741</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="4">
         <v>741</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="4">
         <v>741</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="4">
         <v>741</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B27" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27">
+      <c r="B27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="4">
         <v>1650</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="4">
         <v>1650</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="4">
         <v>1650</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="4">
         <v>1650</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="4">
         <v>1650</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="4">
         <v>1650</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B28" t="s">
-        <v>30</v>
-      </c>
-      <c r="C28">
+      <c r="B28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="4">
         <v>2094</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="4">
         <v>1856</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="4">
         <v>1688</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="4">
         <v>1688</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="4">
         <v>1688</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="4">
         <v>1688</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B29" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29">
+      <c r="B29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="4">
         <v>3630</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="4">
         <v>3630</v>
       </c>
-      <c r="E29">
-        <v>3895</v>
-      </c>
-      <c r="F29">
-        <v>4277</v>
-      </c>
-      <c r="G29">
-        <v>4639</v>
-      </c>
-      <c r="H29">
-        <v>4984</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="E29" s="4">
+        <v>3937</v>
+      </c>
+      <c r="F29" s="4">
+        <v>4325</v>
+      </c>
+      <c r="G29" s="4">
+        <v>4693</v>
+      </c>
+      <c r="H29" s="4">
+        <v>5044</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B30" t="s">
-        <v>30</v>
-      </c>
-      <c r="C30">
-        <v>2970.5</v>
-      </c>
-      <c r="D30">
-        <v>3488</v>
-      </c>
-      <c r="E30">
-        <v>3895</v>
-      </c>
-      <c r="F30">
-        <v>4276.5</v>
-      </c>
-      <c r="G30">
-        <v>4639</v>
-      </c>
-      <c r="H30">
-        <v>4984</v>
+      <c r="B30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="4">
+        <v>3015</v>
+      </c>
+      <c r="D30" s="4">
+        <v>3541.5</v>
+      </c>
+      <c r="E30" s="4">
+        <v>3936.5</v>
+      </c>
+      <c r="F30" s="4">
+        <v>4324.5</v>
+      </c>
+      <c r="G30" s="4">
+        <v>4693</v>
+      </c>
+      <c r="H30" s="4">
+        <v>5043.5</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C9:H9">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
+      <formula>14</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C10:H10">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+      <formula>16</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C21:H21">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>4200</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C22:H22">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+      <formula>12</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/program/ConstructionResults.xlsx
+++ b/program/ConstructionResults.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="472" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="944" uniqueCount="35">
   <si>
     <t>Величина</t>
   </si>
@@ -708,16 +708,16 @@
         <v>31</v>
       </c>
       <c r="C6" s="4">
-        <v>15960</v>
+        <v>16080</v>
       </c>
       <c r="D6" s="4">
-        <v>13320</v>
+        <v>13440</v>
       </c>
       <c r="E6" s="4">
-        <v>11400</v>
+        <v>11520</v>
       </c>
       <c r="F6" s="4">
-        <v>9960</v>
+        <v>10080</v>
       </c>
       <c r="G6" s="4">
         <v>8880</v>
@@ -760,16 +760,16 @@
         <v>31</v>
       </c>
       <c r="C8" s="4">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D8" s="4">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E8" s="4">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F8" s="4">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G8" s="4">
         <v>74</v>
@@ -786,22 +786,22 @@
         <v>32</v>
       </c>
       <c r="C9" s="5">
-        <v>7.7918110583391007</v>
+        <v>7.7341860937132605</v>
       </c>
       <c r="D9" s="5">
-        <v>8.94625441732612</v>
+        <v>8.8669191026249177</v>
       </c>
       <c r="E9" s="5">
-        <v>10.115715250031071</v>
+        <v>10.010903165654847</v>
       </c>
       <c r="F9" s="5">
-        <v>11.279728950072325</v>
+        <v>11.146022414066474</v>
       </c>
       <c r="G9" s="5">
-        <v>12.384183505752892</v>
+        <v>12.384779219527303</v>
       </c>
       <c r="H9" s="5">
-        <v>13.436168418639737</v>
+        <v>13.436773802291452</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
@@ -812,22 +812,22 @@
         <v>32</v>
       </c>
       <c r="C10" s="5">
-        <v>12.674569646000879</v>
+        <v>12.645223440969783</v>
       </c>
       <c r="D10" s="5">
-        <v>13.218448877374112</v>
+        <v>13.167392322267652</v>
       </c>
       <c r="E10" s="5">
-        <v>13.956015927177521</v>
+        <v>13.866628620762064</v>
       </c>
       <c r="F10" s="5">
-        <v>15.120029627218774</v>
+        <v>14.986323091212924</v>
       </c>
       <c r="G10" s="5">
-        <v>16.224484182899342</v>
+        <v>16.225079896673751</v>
       </c>
       <c r="H10" s="5">
-        <v>17.276469095786187</v>
+        <v>17.2770744794379</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
@@ -838,22 +838,22 @@
         <v>32</v>
       </c>
       <c r="C11" s="5">
-        <v>6.5060524706773206</v>
+        <v>6.4421487464567369</v>
       </c>
       <c r="D11" s="5">
-        <v>7.7960599572781284</v>
+        <v>7.7104458829821825</v>
       </c>
       <c r="E11" s="5">
-        <v>9.0614145728846225</v>
+        <v>8.953177710547628</v>
       </c>
       <c r="F11" s="5">
-        <v>10.225428272925877</v>
+        <v>10.091721736920025</v>
       </c>
       <c r="G11" s="5">
-        <v>11.329882828606443</v>
+        <v>11.330478542380854</v>
       </c>
       <c r="H11" s="5">
-        <v>12.381867741493288</v>
+        <v>12.382473125145003</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
@@ -864,16 +864,16 @@
         <v>30</v>
       </c>
       <c r="C12" s="4">
-        <v>11466</v>
+        <v>11423</v>
       </c>
       <c r="D12" s="4">
-        <v>12329</v>
+        <v>12264</v>
       </c>
       <c r="E12" s="4">
-        <v>13292</v>
+        <v>13196</v>
       </c>
       <c r="F12" s="4">
-        <v>14456</v>
+        <v>14323</v>
       </c>
       <c r="G12" s="4">
         <v>15561</v>
@@ -942,16 +942,16 @@
         <v>30</v>
       </c>
       <c r="C15" s="4">
-        <v>2867</v>
+        <v>2889</v>
       </c>
       <c r="D15" s="4">
-        <v>2392</v>
+        <v>2414</v>
       </c>
       <c r="E15" s="4">
-        <v>2046</v>
+        <v>2068</v>
       </c>
       <c r="F15" s="4">
-        <v>1787</v>
+        <v>1809</v>
       </c>
       <c r="G15" s="4">
         <v>1593</v>
@@ -1072,16 +1072,16 @@
         <v>30</v>
       </c>
       <c r="C20" s="4">
-        <v>4517</v>
+        <v>4539</v>
       </c>
       <c r="D20" s="4">
-        <v>4042</v>
+        <v>4064</v>
       </c>
       <c r="E20" s="4">
-        <v>3696</v>
+        <v>3718</v>
       </c>
       <c r="F20" s="4">
-        <v>3437</v>
+        <v>3459</v>
       </c>
       <c r="G20" s="4">
         <v>3243</v>
@@ -1098,13 +1098,13 @@
         <v>30</v>
       </c>
       <c r="C21" s="4">
-        <v>4517</v>
+        <v>4539</v>
       </c>
       <c r="D21" s="4">
-        <v>4042</v>
+        <v>4064</v>
       </c>
       <c r="E21" s="4">
-        <v>3706</v>
+        <v>3718</v>
       </c>
       <c r="F21" s="4">
         <v>3706</v>
@@ -1124,22 +1124,22 @@
         <v>33</v>
       </c>
       <c r="C22" s="5">
-        <v>17.954394509630287</v>
+        <v>18.352059925093634</v>
       </c>
       <c r="D22" s="5">
-        <v>7.4385654195262347</v>
+        <v>7.8871998237497243</v>
       </c>
       <c r="E22" s="5">
-        <v>0.22138587558113793</v>
+        <v>0.26437541308658291</v>
       </c>
       <c r="F22" s="5">
-        <v>5.9552800531326105</v>
+        <v>5.4417272526988327</v>
       </c>
       <c r="G22" s="5">
-        <v>10.250166039406686</v>
+        <v>10.200484688257326</v>
       </c>
       <c r="H22" s="5">
-        <v>13.593092760681868</v>
+        <v>13.527208636263493</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.25">
@@ -1228,13 +1228,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="4">
-        <v>903</v>
+        <v>908</v>
       </c>
       <c r="D26" s="4">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="E26" s="4">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="F26" s="4">
         <v>741</v>
@@ -1280,13 +1280,13 @@
         <v>30</v>
       </c>
       <c r="C28" s="4">
-        <v>2094</v>
+        <v>2105</v>
       </c>
       <c r="D28" s="4">
-        <v>1856</v>
+        <v>1867</v>
       </c>
       <c r="E28" s="4">
-        <v>1688</v>
+        <v>1694</v>
       </c>
       <c r="F28" s="4">
         <v>1688</v>
@@ -1312,10 +1312,10 @@
         <v>3630</v>
       </c>
       <c r="E29" s="4">
-        <v>3937</v>
+        <v>3903</v>
       </c>
       <c r="F29" s="4">
-        <v>4325</v>
+        <v>4280</v>
       </c>
       <c r="G29" s="4">
         <v>4693</v>
@@ -1332,16 +1332,16 @@
         <v>30</v>
       </c>
       <c r="C30" s="4">
-        <v>3015</v>
+        <v>2988.5</v>
       </c>
       <c r="D30" s="4">
-        <v>3541.5</v>
+        <v>3504</v>
       </c>
       <c r="E30" s="4">
-        <v>3936.5</v>
+        <v>3902.5</v>
       </c>
       <c r="F30" s="4">
-        <v>4324.5</v>
+        <v>4280.5</v>
       </c>
       <c r="G30" s="4">
         <v>4693</v>

--- a/program/ConstructionResults.xlsx
+++ b/program/ConstructionResults.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="944" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1062" uniqueCount="35">
   <si>
     <t>Величина</t>
   </si>
@@ -708,16 +708,16 @@
         <v>31</v>
       </c>
       <c r="C6" s="4">
-        <v>16080</v>
+        <v>15960</v>
       </c>
       <c r="D6" s="4">
-        <v>13440</v>
+        <v>13320</v>
       </c>
       <c r="E6" s="4">
-        <v>11520</v>
+        <v>11400</v>
       </c>
       <c r="F6" s="4">
-        <v>10080</v>
+        <v>9960</v>
       </c>
       <c r="G6" s="4">
         <v>8880</v>
@@ -760,16 +760,16 @@
         <v>31</v>
       </c>
       <c r="C8" s="4">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D8" s="4">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E8" s="4">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F8" s="4">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G8" s="4">
         <v>74</v>
@@ -786,22 +786,22 @@
         <v>32</v>
       </c>
       <c r="C9" s="5">
-        <v>7.7341860937132605</v>
+        <v>7.9257398747473076</v>
       </c>
       <c r="D9" s="5">
-        <v>8.8669191026249177</v>
+        <v>9.1071011398718511</v>
       </c>
       <c r="E9" s="5">
-        <v>10.010903165654847</v>
+        <v>10.303991920489274</v>
       </c>
       <c r="F9" s="5">
-        <v>11.146022414066474</v>
+        <v>11.495539442259844</v>
       </c>
       <c r="G9" s="5">
-        <v>12.384779219527303</v>
+        <v>12.626530834362097</v>
       </c>
       <c r="H9" s="5">
-        <v>13.436773802291452</v>
+        <v>13.704104611223888</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
@@ -812,22 +812,22 @@
         <v>32</v>
       </c>
       <c r="C10" s="5">
-        <v>12.645223440969783</v>
+        <v>12.808498462409087</v>
       </c>
       <c r="D10" s="5">
-        <v>13.167392322267652</v>
+        <v>13.379295599919843</v>
       </c>
       <c r="E10" s="5">
-        <v>13.866628620762064</v>
+        <v>14.144292597635722</v>
       </c>
       <c r="F10" s="5">
-        <v>14.986323091212924</v>
+        <v>15.335840119406292</v>
       </c>
       <c r="G10" s="5">
-        <v>16.225079896673751</v>
+        <v>16.466831511508545</v>
       </c>
       <c r="H10" s="5">
-        <v>17.2770744794379</v>
+        <v>17.544405288370339</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
@@ -838,22 +838,22 @@
         <v>32</v>
       </c>
       <c r="C11" s="5">
-        <v>6.4421487464567369</v>
+        <v>6.6399812870855284</v>
       </c>
       <c r="D11" s="5">
-        <v>7.7104458829821825</v>
+        <v>7.9569066798238595</v>
       </c>
       <c r="E11" s="5">
-        <v>8.953177710547628</v>
+        <v>9.2496912433428253</v>
       </c>
       <c r="F11" s="5">
-        <v>10.091721736920025</v>
+        <v>10.441238765113395</v>
       </c>
       <c r="G11" s="5">
-        <v>11.330478542380854</v>
+        <v>11.572230157215648</v>
       </c>
       <c r="H11" s="5">
-        <v>12.382473125145003</v>
+        <v>12.64980393407744</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
@@ -864,22 +864,22 @@
         <v>30</v>
       </c>
       <c r="C12" s="4">
-        <v>11423</v>
+        <v>11600</v>
       </c>
       <c r="D12" s="4">
-        <v>12264</v>
+        <v>12490</v>
       </c>
       <c r="E12" s="4">
-        <v>13196</v>
+        <v>13480</v>
       </c>
       <c r="F12" s="4">
-        <v>14323</v>
+        <v>14672</v>
       </c>
       <c r="G12" s="4">
-        <v>15561</v>
+        <v>15803</v>
       </c>
       <c r="H12" s="4">
-        <v>16613</v>
+        <v>16881</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
@@ -942,16 +942,16 @@
         <v>30</v>
       </c>
       <c r="C15" s="4">
-        <v>2889</v>
+        <v>2867</v>
       </c>
       <c r="D15" s="4">
-        <v>2414</v>
+        <v>2392</v>
       </c>
       <c r="E15" s="4">
-        <v>2068</v>
+        <v>2046</v>
       </c>
       <c r="F15" s="4">
-        <v>1809</v>
+        <v>1787</v>
       </c>
       <c r="G15" s="4">
         <v>1593</v>
@@ -1072,16 +1072,16 @@
         <v>30</v>
       </c>
       <c r="C20" s="4">
-        <v>4539</v>
+        <v>4517</v>
       </c>
       <c r="D20" s="4">
-        <v>4064</v>
+        <v>4042</v>
       </c>
       <c r="E20" s="4">
-        <v>3718</v>
+        <v>3696</v>
       </c>
       <c r="F20" s="4">
-        <v>3459</v>
+        <v>3437</v>
       </c>
       <c r="G20" s="4">
         <v>3243</v>
@@ -1098,13 +1098,13 @@
         <v>30</v>
       </c>
       <c r="C21" s="4">
-        <v>4539</v>
+        <v>4517</v>
       </c>
       <c r="D21" s="4">
-        <v>4064</v>
+        <v>4042</v>
       </c>
       <c r="E21" s="4">
-        <v>3718</v>
+        <v>3706</v>
       </c>
       <c r="F21" s="4">
         <v>3706</v>
@@ -1124,22 +1124,22 @@
         <v>33</v>
       </c>
       <c r="C22" s="5">
-        <v>18.352059925093634</v>
+        <v>17.954394509630287</v>
       </c>
       <c r="D22" s="5">
-        <v>7.8871998237497243</v>
+        <v>7.4385654195262347</v>
       </c>
       <c r="E22" s="5">
-        <v>0.26437541308658291</v>
+        <v>0.22138587558113793</v>
       </c>
       <c r="F22" s="5">
-        <v>5.4417272526988327</v>
+        <v>5.9552800531326105</v>
       </c>
       <c r="G22" s="5">
-        <v>10.200484688257326</v>
+        <v>10.250166039406686</v>
       </c>
       <c r="H22" s="5">
-        <v>13.527208636263493</v>
+        <v>13.593092760681868</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.25">
@@ -1228,13 +1228,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="4">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="D26" s="4">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="E26" s="4">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="F26" s="4">
         <v>741</v>
@@ -1280,13 +1280,13 @@
         <v>30</v>
       </c>
       <c r="C28" s="4">
-        <v>2105</v>
+        <v>2094</v>
       </c>
       <c r="D28" s="4">
-        <v>1867</v>
+        <v>1856</v>
       </c>
       <c r="E28" s="4">
-        <v>1694</v>
+        <v>1688</v>
       </c>
       <c r="F28" s="4">
         <v>1688</v>
@@ -1312,16 +1312,16 @@
         <v>3630</v>
       </c>
       <c r="E29" s="4">
-        <v>3903</v>
+        <v>3999</v>
       </c>
       <c r="F29" s="4">
-        <v>4280</v>
+        <v>4397</v>
       </c>
       <c r="G29" s="4">
-        <v>4693</v>
+        <v>4774</v>
       </c>
       <c r="H29" s="4">
-        <v>5044</v>
+        <v>5133</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.25">
@@ -1332,22 +1332,22 @@
         <v>30</v>
       </c>
       <c r="C30" s="4">
-        <v>2988.5</v>
+        <v>3082</v>
       </c>
       <c r="D30" s="4">
-        <v>3504</v>
+        <v>3622</v>
       </c>
       <c r="E30" s="4">
-        <v>3902.5</v>
+        <v>3999.5</v>
       </c>
       <c r="F30" s="4">
-        <v>4280.5</v>
+        <v>4396.5</v>
       </c>
       <c r="G30" s="4">
-        <v>4693</v>
+        <v>4773.5</v>
       </c>
       <c r="H30" s="4">
-        <v>5043.5</v>
+        <v>5133</v>
       </c>
     </row>
   </sheetData>

--- a/program/ConstructionResults.xlsx
+++ b/program/ConstructionResults.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1062" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1121" uniqueCount="35">
   <si>
     <t>Величина</t>
   </si>

--- a/program/ConstructionResults.xlsx
+++ b/program/ConstructionResults.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1121" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1239" uniqueCount="35">
   <si>
     <t>Величина</t>
   </si>

--- a/program/ConstructionResults.xlsx
+++ b/program/ConstructionResults.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1239" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1298" uniqueCount="35">
   <si>
     <t>Величина</t>
   </si>

--- a/program/ConstructionResults.xlsx
+++ b/program/ConstructionResults.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1298" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1357" uniqueCount="35">
   <si>
     <t>Величина</t>
   </si>
